--- a/pipeline_output/companies_pipeline.xlsx
+++ b/pipeline_output/companies_pipeline.xlsx
@@ -1,12 +1,12 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Companies Pipeline" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Companies Pipeline" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="0" fullCalcOnLoad="1"/>
@@ -438,7 +438,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB13"/>
+  <dimension ref="A1:AB16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -461,8 +461,8 @@
     <col width="50" customWidth="1" min="19" max="19"/>
     <col width="29" customWidth="1" min="20" max="20"/>
     <col width="15" customWidth="1" min="21" max="21"/>
-    <col width="13" customWidth="1" min="22" max="22"/>
-    <col width="31" customWidth="1" min="23" max="23"/>
+    <col width="28.5703125" customWidth="1" min="22" max="22"/>
+    <col width="30.7109375" bestFit="1" customWidth="1" min="23" max="23"/>
     <col width="21" customWidth="1" min="24" max="24"/>
   </cols>
   <sheetData>
@@ -1064,12 +1064,12 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>drzoebell@gmail.com</t>
+          <t>edwardburi26@gmail.com</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>Drzo Ebell</t>
+          <t>Edwar Dburi</t>
         </is>
       </c>
     </row>
@@ -1482,16 +1482,6 @@
           <t>skipped</t>
         </is>
       </c>
-      <c r="W9" t="inlineStr">
-        <is>
-          <t>edwardburi26@gmail.com</t>
-        </is>
-      </c>
-      <c r="X9" t="inlineStr">
-        <is>
-          <t>Edwar Dburi</t>
-        </is>
-      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1739,6 +1729,190 @@
       <c r="S13" t="inlineStr">
         <is>
           <t>D:\Company Registrations\pipeline_output\companies\16607960 - KAMAU GROUP LTD\certificate\Certificate_16607960.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>11993440</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>NEEMA NDUNGU LTD</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>86900</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>9 Piper Close, Wellingborough, NN8 4US, England</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>NJONJO, Neema</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>British</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>225067762</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>found</t>
+        </is>
+      </c>
+      <c r="R14" t="b">
+        <v>1</v>
+      </c>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>D:\Company Registrations\pipeline_output\companies\11993440 - NEEMA NDUNGU LTD\certificate\Certificate_11993440.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>14</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>16401657</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>MBUGUA GITAU LTD</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>43290, 43999</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>79 Stonehills, Rugby, CV21 1NB, England</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>GITAU, Augustine Mbugua</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>Kenyan</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>233732527</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>found</t>
+        </is>
+      </c>
+      <c r="R15" t="b">
+        <v>1</v>
+      </c>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>D:\Company Registrations\pipeline_output\companies\16401657 - MBUGUA GITAU LTD\certificate\Certificate_16401657.pdf</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>eveaurora41@gmail.com</t>
+        </is>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>Evea Urora</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>15</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>10793456</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>MWENE SERVICES LTD</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>82990</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>10 Bedford Heights 2 Bedford Road, Luton, LU2 7NZ, England</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>NYAGA, Moses Mwangi</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>Kenyan</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>222998793</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>found</t>
+        </is>
+      </c>
+      <c r="R16" t="b">
+        <v>1</v>
+      </c>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>D:\Company Registrations\pipeline_output\companies\10793456 - MWENE SERVICES LTD\certificate\Certificate_10793456.pdf</t>
         </is>
       </c>
     </row>
